--- a/输出/上海高中物理-考点公式清单.xlsx
+++ b/输出/上海高中物理-考点公式清单.xlsx
@@ -25879,7 +25879,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>R测 = R_xR_V/(R_x+R_V)</t>
+          <t>R测 = R_x·R_V/(R_x+R_V)</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
